--- a/T388_Excel.xlsx
+++ b/T388_Excel.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Admin\OneDrive\Documents\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{6DC3E94D-681C-4C8E-85C8-115E3BB76200}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C66B3319-CA99-40F9-AD17-B862824B3904}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{97914E35-3EC5-46A0-9D29-D522FBEA4F09}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="30" uniqueCount="24">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="23" uniqueCount="23">
   <si>
     <t>ID</t>
   </si>
@@ -45,9 +45,6 @@
     <t>SALARY</t>
   </si>
   <si>
-    <t>Ajit</t>
-  </si>
-  <si>
     <t>Suman</t>
   </si>
   <si>
@@ -84,35 +81,35 @@
     <t>TOTAL SALARY</t>
   </si>
   <si>
-    <t>Maharashtra</t>
-  </si>
-  <si>
-    <t>Gujrat</t>
-  </si>
-  <si>
-    <t>UP</t>
-  </si>
-  <si>
-    <t>Goa</t>
-  </si>
-  <si>
-    <t>Chennai</t>
-  </si>
-  <si>
-    <t>MP</t>
-  </si>
-  <si>
     <t>ctrl+N</t>
   </si>
   <si>
     <t>NEW FILE</t>
+  </si>
+  <si>
+    <t>Ajit Kumar</t>
+  </si>
+  <si>
+    <t>ctrl+f</t>
+  </si>
+  <si>
+    <t>To Find</t>
+  </si>
+  <si>
+    <t>ctrl+h</t>
+  </si>
+  <si>
+    <t>To Replace</t>
+  </si>
+  <si>
+    <t>Aniket</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -137,6 +134,13 @@
     </font>
     <font>
       <sz val="8"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -183,7 +187,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -195,8 +199,13 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -526,7 +535,7 @@
         <v>0</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C1" s="2" t="s">
         <v>1</v>
@@ -535,16 +544,16 @@
         <v>2</v>
       </c>
       <c r="E1" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F1" s="2" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="I1" t="s">
+        <v>7</v>
+      </c>
+      <c r="J1" t="s">
         <v>8</v>
-      </c>
-      <c r="J1" t="s">
-        <v>9</v>
       </c>
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.3">
@@ -555,7 +564,7 @@
         <v>23</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>3</v>
+        <v>22</v>
       </c>
       <c r="D2" s="3">
         <v>23000</v>
@@ -564,15 +573,15 @@
         <f>D2*5%</f>
         <v>1150</v>
       </c>
-      <c r="F2" s="6">
+      <c r="F2" s="5">
         <f>D2+E2</f>
         <v>24150</v>
       </c>
       <c r="I2" t="s">
+        <v>10</v>
+      </c>
+      <c r="J2" t="s">
         <v>11</v>
-      </c>
-      <c r="J2" t="s">
-        <v>12</v>
       </c>
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.3">
@@ -583,24 +592,24 @@
         <v>25</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D3" s="3">
         <v>45000</v>
       </c>
       <c r="E3" s="5">
-        <f t="shared" ref="E3:E5" si="0">D3*5%</f>
+        <f t="shared" ref="E3:E6" si="0">D3*5%</f>
         <v>2250</v>
       </c>
-      <c r="F3" s="6">
-        <f t="shared" ref="F3:F5" si="1">D3+E3</f>
+      <c r="F3" s="5">
+        <f t="shared" ref="F3:F6" si="1">D3+E3</f>
         <v>47250</v>
       </c>
       <c r="I3" t="s">
+        <v>12</v>
+      </c>
+      <c r="J3" t="s">
         <v>13</v>
-      </c>
-      <c r="J3" t="s">
-        <v>14</v>
       </c>
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.3">
@@ -611,7 +620,7 @@
         <v>26</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D4" s="3">
         <v>46000</v>
@@ -620,15 +629,15 @@
         <f t="shared" si="0"/>
         <v>2300</v>
       </c>
-      <c r="F4" s="6">
+      <c r="F4" s="5">
         <f t="shared" si="1"/>
         <v>48300</v>
       </c>
       <c r="I4" t="s">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="J4" t="s">
-        <v>23</v>
+        <v>16</v>
       </c>
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.3">
@@ -639,7 +648,7 @@
         <v>27</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D5" s="3">
         <v>30000</v>
@@ -648,88 +657,80 @@
         <f t="shared" si="0"/>
         <v>1500</v>
       </c>
-      <c r="F5" s="6">
+      <c r="F5" s="5">
         <f t="shared" si="1"/>
         <v>31500</v>
       </c>
-    </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A6" s="1"/>
-      <c r="B6" s="1"/>
-      <c r="C6" s="1"/>
-      <c r="D6" s="1"/>
+      <c r="I5" t="s">
+        <v>18</v>
+      </c>
+      <c r="J5" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A6" s="3">
+        <v>5</v>
+      </c>
+      <c r="B6" s="3">
+        <v>25</v>
+      </c>
+      <c r="C6" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="D6" s="3">
+        <v>25000</v>
+      </c>
+      <c r="E6" s="7">
+        <f t="shared" si="0"/>
+        <v>1250</v>
+      </c>
+      <c r="F6" s="6">
+        <f>D6+E6</f>
+        <v>26250</v>
+      </c>
+      <c r="I6" t="s">
+        <v>20</v>
+      </c>
+      <c r="J6" t="s">
+        <v>21</v>
+      </c>
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A7" s="1"/>
       <c r="B7" s="1"/>
       <c r="C7" s="1"/>
       <c r="D7" s="1"/>
-      <c r="H7" t="s">
-        <v>16</v>
-      </c>
-      <c r="J7" t="s">
-        <v>16</v>
-      </c>
     </row>
     <row r="8" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A8" s="1"/>
       <c r="B8" s="1"/>
       <c r="C8" s="1"/>
       <c r="D8" s="1"/>
-      <c r="H8" t="s">
-        <v>17</v>
-      </c>
-      <c r="J8" t="s">
-        <v>17</v>
-      </c>
     </row>
     <row r="9" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A9" s="1"/>
       <c r="B9" s="1"/>
       <c r="C9" s="1"/>
       <c r="D9" s="1"/>
-      <c r="H9" t="s">
-        <v>18</v>
-      </c>
-      <c r="J9" t="s">
-        <v>18</v>
-      </c>
     </row>
     <row r="10" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A10" s="1"/>
       <c r="B10" s="1"/>
       <c r="C10" s="1"/>
       <c r="D10" s="1"/>
-      <c r="H10" t="s">
-        <v>19</v>
-      </c>
-      <c r="J10" t="s">
-        <v>19</v>
-      </c>
     </row>
     <row r="11" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A11" s="1"/>
       <c r="B11" s="1"/>
       <c r="C11" s="1"/>
       <c r="D11" s="1"/>
-      <c r="H11" t="s">
-        <v>20</v>
-      </c>
-      <c r="J11" t="s">
-        <v>20</v>
-      </c>
     </row>
     <row r="12" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A12" s="1"/>
       <c r="B12" s="1"/>
       <c r="C12" s="1"/>
       <c r="D12" s="1"/>
-      <c r="H12" t="s">
-        <v>21</v>
-      </c>
-      <c r="J12" t="s">
-        <v>21</v>
-      </c>
     </row>
     <row r="13" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A13" s="1"/>

--- a/T388_Excel.xlsx
+++ b/T388_Excel.xlsx
@@ -8,12 +8,14 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Admin\OneDrive\Documents\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C66B3319-CA99-40F9-AD17-B862824B3904}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E30ED5A1-8554-4E9D-8791-3C50885488E3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{97914E35-3EC5-46A0-9D29-D522FBEA4F09}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{97914E35-3EC5-46A0-9D29-D522FBEA4F09}"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="Sheet2" sheetId="2" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" r:id="rId2"/>
+    <sheet name="Sheet3" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -34,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="23" uniqueCount="23">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="68" uniqueCount="54">
   <si>
     <t>ID</t>
   </si>
@@ -103,13 +105,106 @@
   </si>
   <si>
     <t>Aniket</t>
+  </si>
+  <si>
+    <t>Marks</t>
+  </si>
+  <si>
+    <t>ank.23@gmail.com</t>
+  </si>
+  <si>
+    <t>suk.25@gmail.com</t>
+  </si>
+  <si>
+    <t>kik.26@gmail.com</t>
+  </si>
+  <si>
+    <t>amk.27@gmail.com</t>
+  </si>
+  <si>
+    <t>ajk.25@gmail.com</t>
+  </si>
+  <si>
+    <t>Raj</t>
+  </si>
+  <si>
+    <t>GMAILS</t>
+  </si>
+  <si>
+    <t>MONTH</t>
+  </si>
+  <si>
+    <t>SHARE PRICE</t>
+  </si>
+  <si>
+    <t>Mar</t>
+  </si>
+  <si>
+    <t>Apr</t>
+  </si>
+  <si>
+    <t>May</t>
+  </si>
+  <si>
+    <t>June</t>
+  </si>
+  <si>
+    <t>July</t>
+  </si>
+  <si>
+    <t>PRODUCT</t>
+  </si>
+  <si>
+    <t>SOURCE</t>
+  </si>
+  <si>
+    <t>REMARK</t>
+  </si>
+  <si>
+    <t>UNIT PRICE</t>
+  </si>
+  <si>
+    <t>QTY.</t>
+  </si>
+  <si>
+    <t>SALES</t>
+  </si>
+  <si>
+    <t>Banana</t>
+  </si>
+  <si>
+    <t>Apple</t>
+  </si>
+  <si>
+    <t>Tomato</t>
+  </si>
+  <si>
+    <t>Green Peas</t>
+  </si>
+  <si>
+    <t>Cherry</t>
+  </si>
+  <si>
+    <t>Spinach</t>
+  </si>
+  <si>
+    <t>Fresh</t>
+  </si>
+  <si>
+    <t>Frozen</t>
+  </si>
+  <si>
+    <t>Fruit</t>
+  </si>
+  <si>
+    <t>Vegetable</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="9" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -145,8 +240,39 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color theme="10"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="8"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -159,8 +285,14 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="2">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -183,11 +315,23 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -205,11 +349,37 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="15" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
+    <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -521,16 +691,27 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BB60FD70-39C4-4057-8347-98CA45557147}">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetData/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6FC74FB1-AD57-4850-AA87-E06A6A7A96BD}">
-  <dimension ref="A1:J13"/>
+  <dimension ref="A1:K30"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
+    <col min="4" max="4" width="10.5546875" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="13.77734375" style="4" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="17" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="11.77734375" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="11.77734375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -549,6 +730,9 @@
       <c r="F1" s="2" t="s">
         <v>14</v>
       </c>
+      <c r="G1" s="10" t="s">
+        <v>30</v>
+      </c>
       <c r="I1" t="s">
         <v>7</v>
       </c>
@@ -556,7 +740,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A2" s="3">
         <v>1</v>
       </c>
@@ -577,6 +761,9 @@
         <f>D2+E2</f>
         <v>24150</v>
       </c>
+      <c r="G2" s="7" t="s">
+        <v>24</v>
+      </c>
       <c r="I2" t="s">
         <v>10</v>
       </c>
@@ -584,7 +771,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A3" s="3">
         <v>2</v>
       </c>
@@ -602,8 +789,11 @@
         <v>2250</v>
       </c>
       <c r="F3" s="5">
-        <f t="shared" ref="F3:F6" si="1">D3+E3</f>
+        <f t="shared" ref="F3:F5" si="1">D3+E3</f>
         <v>47250</v>
+      </c>
+      <c r="G3" s="7" t="s">
+        <v>25</v>
       </c>
       <c r="I3" t="s">
         <v>12</v>
@@ -612,7 +802,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A4" s="3">
         <v>3</v>
       </c>
@@ -633,6 +823,9 @@
         <f t="shared" si="1"/>
         <v>48300</v>
       </c>
+      <c r="G4" s="7" t="s">
+        <v>26</v>
+      </c>
       <c r="I4" t="s">
         <v>15</v>
       </c>
@@ -640,7 +833,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A5" s="3">
         <v>4</v>
       </c>
@@ -661,6 +854,9 @@
         <f t="shared" si="1"/>
         <v>31500</v>
       </c>
+      <c r="G5" s="7" t="s">
+        <v>27</v>
+      </c>
       <c r="I5" t="s">
         <v>18</v>
       </c>
@@ -668,7 +864,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="6" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:11" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A6" s="3">
         <v>5</v>
       </c>
@@ -681,7 +877,7 @@
       <c r="D6" s="3">
         <v>25000</v>
       </c>
-      <c r="E6" s="7">
+      <c r="E6" s="5">
         <f t="shared" si="0"/>
         <v>1250</v>
       </c>
@@ -689,6 +885,9 @@
         <f>D6+E6</f>
         <v>26250</v>
       </c>
+      <c r="G6" s="7" t="s">
+        <v>28</v>
+      </c>
       <c r="I6" t="s">
         <v>20</v>
       </c>
@@ -696,51 +895,352 @@
         <v>21</v>
       </c>
     </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A7" s="1"/>
       <c r="B7" s="1"/>
       <c r="C7" s="1"/>
       <c r="D7" s="1"/>
     </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A8" s="1"/>
       <c r="B8" s="1"/>
-      <c r="C8" s="1"/>
-      <c r="D8" s="1"/>
-    </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="C8" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="F8" s="11" t="s">
+        <v>31</v>
+      </c>
+      <c r="G8" s="11" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="9" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A9" s="1"/>
       <c r="B9" s="1"/>
-      <c r="C9" s="1"/>
-      <c r="D9" s="1"/>
-    </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="C9" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="D9" s="1">
+        <v>30</v>
+      </c>
+      <c r="F9" s="14">
+        <v>46023</v>
+      </c>
+      <c r="G9" s="12">
+        <v>205</v>
+      </c>
+      <c r="I9">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="10" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A10" s="1"/>
       <c r="B10" s="1"/>
-      <c r="C10" s="1"/>
-      <c r="D10" s="1"/>
-    </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="C10" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="D10" s="1">
+        <v>45</v>
+      </c>
+      <c r="F10" s="14">
+        <v>46054</v>
+      </c>
+      <c r="G10" s="12">
+        <v>206.7</v>
+      </c>
+    </row>
+    <row r="11" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A11" s="1"/>
       <c r="B11" s="1"/>
-      <c r="C11" s="1"/>
-      <c r="D11" s="1"/>
-    </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="C11" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="D11" s="1">
+        <v>44</v>
+      </c>
+      <c r="F11" s="13" t="s">
+        <v>33</v>
+      </c>
+      <c r="G11" s="12">
+        <v>204.3</v>
+      </c>
+    </row>
+    <row r="12" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A12" s="1"/>
       <c r="B12" s="1"/>
-      <c r="C12" s="1"/>
-      <c r="D12" s="1"/>
-    </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="C12" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="D12" s="1">
+        <v>15</v>
+      </c>
+      <c r="F12" s="13" t="s">
+        <v>34</v>
+      </c>
+      <c r="G12" s="12">
+        <v>207.1</v>
+      </c>
+      <c r="I12">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="13" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A13" s="1"/>
       <c r="B13" s="1"/>
-      <c r="C13" s="1"/>
-      <c r="D13" s="1"/>
+      <c r="C13" s="8" t="s">
+        <v>29</v>
+      </c>
+      <c r="D13" s="9">
+        <v>45</v>
+      </c>
+      <c r="F13" s="13" t="s">
+        <v>35</v>
+      </c>
+      <c r="G13" s="12">
+        <v>208.1</v>
+      </c>
+    </row>
+    <row r="14" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="C14" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="D14" s="9">
+        <v>25</v>
+      </c>
+      <c r="F14" s="13" t="s">
+        <v>36</v>
+      </c>
+      <c r="G14" s="12">
+        <v>207.9</v>
+      </c>
+      <c r="K14">
+        <f>I9*5</f>
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="15" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="F15" s="13" t="s">
+        <v>37</v>
+      </c>
+      <c r="G15" s="12">
+        <v>208.2</v>
+      </c>
+    </row>
+    <row r="16" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="K16">
+        <f>I12*6</f>
+        <v>2400</v>
+      </c>
+    </row>
+    <row r="17" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="I17">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="20" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="K20">
+        <f>I17+55</f>
+        <v>1055</v>
+      </c>
+    </row>
+    <row r="23" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A23" s="15" t="s">
+        <v>38</v>
+      </c>
+      <c r="B23" s="15" t="s">
+        <v>39</v>
+      </c>
+      <c r="C23" s="15" t="s">
+        <v>40</v>
+      </c>
+      <c r="D23" s="15" t="s">
+        <v>41</v>
+      </c>
+      <c r="E23" s="15" t="s">
+        <v>42</v>
+      </c>
+      <c r="F23" s="15" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="24" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A24" s="12" t="s">
+        <v>44</v>
+      </c>
+      <c r="B24" s="12" t="s">
+        <v>50</v>
+      </c>
+      <c r="C24" s="12" t="s">
+        <v>52</v>
+      </c>
+      <c r="D24" s="12">
+        <v>40</v>
+      </c>
+      <c r="E24" s="12">
+        <v>2</v>
+      </c>
+      <c r="F24" s="16">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="25" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A25" s="12" t="s">
+        <v>45</v>
+      </c>
+      <c r="B25" s="12" t="s">
+        <v>51</v>
+      </c>
+      <c r="C25" s="12" t="s">
+        <v>52</v>
+      </c>
+      <c r="D25" s="12">
+        <v>120</v>
+      </c>
+      <c r="E25" s="12">
+        <v>2</v>
+      </c>
+      <c r="F25" s="16">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="26" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A26" s="12" t="s">
+        <v>46</v>
+      </c>
+      <c r="B26" s="12" t="s">
+        <v>50</v>
+      </c>
+      <c r="C26" s="12" t="s">
+        <v>53</v>
+      </c>
+      <c r="D26" s="12">
+        <v>60</v>
+      </c>
+      <c r="E26" s="12">
+        <v>4</v>
+      </c>
+      <c r="F26" s="16">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="27" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A27" s="12" t="s">
+        <v>47</v>
+      </c>
+      <c r="B27" s="12" t="s">
+        <v>51</v>
+      </c>
+      <c r="C27" s="12" t="s">
+        <v>53</v>
+      </c>
+      <c r="D27" s="12">
+        <v>100</v>
+      </c>
+      <c r="E27" s="12">
+        <v>3</v>
+      </c>
+      <c r="F27" s="16">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="28" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A28" s="12" t="s">
+        <v>48</v>
+      </c>
+      <c r="B28" s="12" t="s">
+        <v>51</v>
+      </c>
+      <c r="C28" s="12" t="s">
+        <v>52</v>
+      </c>
+      <c r="D28" s="12">
+        <v>120</v>
+      </c>
+      <c r="E28" s="12">
+        <v>6</v>
+      </c>
+      <c r="F28" s="16">
+        <v>720</v>
+      </c>
+    </row>
+    <row r="29" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A29" s="12" t="s">
+        <v>49</v>
+      </c>
+      <c r="B29" s="12" t="s">
+        <v>51</v>
+      </c>
+      <c r="C29" s="12" t="s">
+        <v>53</v>
+      </c>
+      <c r="D29" s="12">
+        <v>25</v>
+      </c>
+      <c r="E29" s="12">
+        <v>2</v>
+      </c>
+      <c r="F29" s="16">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="30" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A30" s="12"/>
     </row>
   </sheetData>
   <phoneticPr fontId="3" type="noConversion"/>
+  <conditionalFormatting sqref="D8:D14">
+    <cfRule type="dataBar" priority="4">
+      <dataBar>
+        <cfvo type="min"/>
+        <cfvo type="max"/>
+        <color rgb="FF638EC6"/>
+      </dataBar>
+      <extLst>
+        <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
+          <x14:id>{48A0BBBF-327F-4F1E-9441-CADF718150DB}</x14:id>
+        </ext>
+      </extLst>
+    </cfRule>
+  </conditionalFormatting>
+  <hyperlinks>
+    <hyperlink ref="G2" r:id="rId1" xr:uid="{8CDFE076-B84D-47F7-81DC-EBE01424DE7D}"/>
+    <hyperlink ref="G3" r:id="rId2" xr:uid="{37DF5225-85FB-4F03-81A8-4A159C453842}"/>
+    <hyperlink ref="G4" r:id="rId3" xr:uid="{450BF1C8-AF3C-42FA-A402-88E9E5A8AD6E}"/>
+    <hyperlink ref="G5" r:id="rId4" xr:uid="{D09DE00B-C751-41DE-9407-23E1A969194B}"/>
+    <hyperlink ref="G6" r:id="rId5" xr:uid="{CE0B6BFB-416D-4DC4-89A9-32AEA3FCD8B9}"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" r:id="rId1"/>
+  <pageSetup orientation="portrait" r:id="rId6"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{78C0D931-6437-407d-A8EE-F0AAD7539E65}">
+      <x14:conditionalFormattings>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="dataBar" id="{48A0BBBF-327F-4F1E-9441-CADF718150DB}">
+            <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
+              <x14:cfvo type="autoMin"/>
+              <x14:cfvo type="autoMax"/>
+              <x14:borderColor rgb="FF638EC6"/>
+              <x14:negativeFillColor rgb="FFFF0000"/>
+              <x14:negativeBorderColor rgb="FFFF0000"/>
+              <x14:axisColor rgb="FF000000"/>
+            </x14:dataBar>
+          </x14:cfRule>
+          <xm:sqref>D8:D14</xm:sqref>
+        </x14:conditionalFormatting>
+      </x14:conditionalFormattings>
+    </ext>
+  </extLst>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0AB9FC98-78AE-4240-86AF-DAC89B581F95}">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetData/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/T388_Excel.xlsx
+++ b/T388_Excel.xlsx
@@ -8,14 +8,12 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Admin\OneDrive\Documents\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E30ED5A1-8554-4E9D-8791-3C50885488E3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A7D3DCB0-3088-46CA-B55D-1F93149D8A81}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{97914E35-3EC5-46A0-9D29-D522FBEA4F09}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{97914E35-3EC5-46A0-9D29-D522FBEA4F09}"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet2" sheetId="2" r:id="rId1"/>
-    <sheet name="Sheet1" sheetId="1" r:id="rId2"/>
-    <sheet name="Sheet3" sheetId="3" r:id="rId3"/>
+    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -36,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="68" uniqueCount="54">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="87" uniqueCount="50">
   <si>
     <t>ID</t>
   </si>
@@ -137,21 +135,6 @@
     <t>SHARE PRICE</t>
   </si>
   <si>
-    <t>Mar</t>
-  </si>
-  <si>
-    <t>Apr</t>
-  </si>
-  <si>
-    <t>May</t>
-  </si>
-  <si>
-    <t>June</t>
-  </si>
-  <si>
-    <t>July</t>
-  </si>
-  <si>
     <t>PRODUCT</t>
   </si>
   <si>
@@ -198,6 +181,9 @@
   </si>
   <si>
     <t>Vegetable</t>
+  </si>
+  <si>
+    <t>F21</t>
   </si>
 </sst>
 </file>
@@ -331,7 +317,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -350,10 +336,7 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -365,16 +348,10 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="15" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -691,17 +668,8 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BB60FD70-39C4-4057-8347-98CA45557147}">
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
-  <sheetData/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6FC74FB1-AD57-4850-AA87-E06A6A7A96BD}">
-  <dimension ref="A1:K30"/>
+  <dimension ref="A1:X32"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="4" max="4" width="10.5546875" bestFit="1" customWidth="1"/>
@@ -709,9 +677,12 @@
     <col min="7" max="7" width="17" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="11.77734375" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="11.77734375" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="10.21875" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="9.33203125" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="10.5546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -730,7 +701,7 @@
       <c r="F1" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="G1" s="10" t="s">
+      <c r="G1" s="9" t="s">
         <v>30</v>
       </c>
       <c r="I1" t="s">
@@ -739,8 +710,29 @@
       <c r="J1" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="O1" s="13" t="s">
+        <v>33</v>
+      </c>
+      <c r="P1" s="13" t="s">
+        <v>34</v>
+      </c>
+      <c r="Q1" s="13" t="s">
+        <v>35</v>
+      </c>
+      <c r="R1" s="13" t="s">
+        <v>36</v>
+      </c>
+      <c r="S1" s="13" t="s">
+        <v>37</v>
+      </c>
+      <c r="T1" s="13" t="s">
+        <v>38</v>
+      </c>
+      <c r="W1" s="11">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="2" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A2" s="3">
         <v>1</v>
       </c>
@@ -770,8 +762,29 @@
       <c r="J2" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="O2" s="11" t="s">
+        <v>39</v>
+      </c>
+      <c r="P2" s="11" t="s">
+        <v>45</v>
+      </c>
+      <c r="Q2" s="11" t="s">
+        <v>47</v>
+      </c>
+      <c r="R2" s="11">
+        <v>40</v>
+      </c>
+      <c r="S2" s="11">
+        <v>2</v>
+      </c>
+      <c r="T2" s="11">
+        <v>80</v>
+      </c>
+      <c r="W2" s="11">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="3" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A3" s="3">
         <v>2</v>
       </c>
@@ -801,8 +814,33 @@
       <c r="J3" t="s">
         <v>13</v>
       </c>
-    </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="O3" s="11" t="s">
+        <v>40</v>
+      </c>
+      <c r="P3" s="11" t="s">
+        <v>46</v>
+      </c>
+      <c r="Q3" s="11" t="s">
+        <v>47</v>
+      </c>
+      <c r="R3" s="11">
+        <v>120</v>
+      </c>
+      <c r="S3" s="11">
+        <v>2</v>
+      </c>
+      <c r="T3" s="11">
+        <v>240</v>
+      </c>
+      <c r="W3" s="11" t="b">
+        <v>1</v>
+      </c>
+      <c r="X3">
+        <f>COUNTA(W1:W6)</f>
+        <v>6</v>
+      </c>
+    </row>
+    <row r="4" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A4" s="3">
         <v>3</v>
       </c>
@@ -832,8 +870,33 @@
       <c r="J4" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="O4" s="11" t="s">
+        <v>41</v>
+      </c>
+      <c r="P4" s="11" t="s">
+        <v>45</v>
+      </c>
+      <c r="Q4" s="11" t="s">
+        <v>48</v>
+      </c>
+      <c r="R4" s="11">
+        <v>60</v>
+      </c>
+      <c r="S4" s="11">
+        <v>4</v>
+      </c>
+      <c r="T4" s="11">
+        <v>240</v>
+      </c>
+      <c r="W4" s="11">
+        <v>25</v>
+      </c>
+      <c r="X4">
+        <f>COUNTBLANK(W1:W6)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A5" s="3">
         <v>4</v>
       </c>
@@ -863,8 +926,29 @@
       <c r="J5" t="s">
         <v>19</v>
       </c>
-    </row>
-    <row r="6" spans="1:11" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="O5" s="11" t="s">
+        <v>42</v>
+      </c>
+      <c r="P5" s="11" t="s">
+        <v>46</v>
+      </c>
+      <c r="Q5" s="11" t="s">
+        <v>48</v>
+      </c>
+      <c r="R5" s="11">
+        <v>100</v>
+      </c>
+      <c r="S5" s="11">
+        <v>3</v>
+      </c>
+      <c r="T5" s="11">
+        <v>300</v>
+      </c>
+      <c r="W5" s="11" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="6" spans="1:24" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A6" s="3">
         <v>5</v>
       </c>
@@ -894,14 +978,53 @@
       <c r="J6" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="O6" s="11" t="s">
+        <v>43</v>
+      </c>
+      <c r="P6" s="11" t="s">
+        <v>46</v>
+      </c>
+      <c r="Q6" s="11" t="s">
+        <v>47</v>
+      </c>
+      <c r="R6" s="11">
+        <v>120</v>
+      </c>
+      <c r="S6" s="11">
+        <v>6</v>
+      </c>
+      <c r="T6" s="11">
+        <v>720</v>
+      </c>
+      <c r="W6" s="11">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="7" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A7" s="1"/>
       <c r="B7" s="1"/>
       <c r="C7" s="1"/>
       <c r="D7" s="1"/>
-    </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="O7" s="11" t="s">
+        <v>44</v>
+      </c>
+      <c r="P7" s="11" t="s">
+        <v>46</v>
+      </c>
+      <c r="Q7" s="11" t="s">
+        <v>48</v>
+      </c>
+      <c r="R7" s="11">
+        <v>25</v>
+      </c>
+      <c r="S7" s="11">
+        <v>2</v>
+      </c>
+      <c r="T7" s="11">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="8" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A8" s="1"/>
       <c r="B8" s="1"/>
       <c r="C8" s="2" t="s">
@@ -910,14 +1033,14 @@
       <c r="D8" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="F8" s="11" t="s">
+      <c r="F8" s="10" t="s">
         <v>31</v>
       </c>
-      <c r="G8" s="11" t="s">
+      <c r="G8" s="10" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A9" s="1"/>
       <c r="B9" s="1"/>
       <c r="C9" s="3" t="s">
@@ -926,17 +1049,25 @@
       <c r="D9" s="1">
         <v>30</v>
       </c>
-      <c r="F9" s="14">
+      <c r="F9" s="12">
         <v>46023</v>
       </c>
-      <c r="G9" s="12">
+      <c r="G9" s="11">
         <v>205</v>
       </c>
       <c r="I9">
         <v>200</v>
       </c>
-    </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="Q9">
+        <f>COUNTIF(Q2:Q7,"Fruit")</f>
+        <v>3</v>
+      </c>
+      <c r="R9">
+        <f>SUMIF(Q2:Q7,"Fruit",S2:S7)</f>
+        <v>10</v>
+      </c>
+    </row>
+    <row r="10" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A10" s="1"/>
       <c r="B10" s="1"/>
       <c r="C10" s="3" t="s">
@@ -945,14 +1076,22 @@
       <c r="D10" s="1">
         <v>45</v>
       </c>
-      <c r="F10" s="14">
+      <c r="F10" s="12">
         <v>46054</v>
       </c>
-      <c r="G10" s="12">
+      <c r="G10" s="11">
         <v>206.7</v>
       </c>
-    </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="Q10">
+        <f>COUNTIFS(P2:P7,"Frozen",Q2:Q7,"vegetable")</f>
+        <v>2</v>
+      </c>
+      <c r="R10">
+        <f>SUMIFS(S2:S7,P2:P7,"Frozen",Q2:Q7,"Fruit")</f>
+        <v>8</v>
+      </c>
+    </row>
+    <row r="11" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A11" s="1"/>
       <c r="B11" s="1"/>
       <c r="C11" s="3" t="s">
@@ -961,14 +1100,18 @@
       <c r="D11" s="1">
         <v>44</v>
       </c>
-      <c r="F11" s="13" t="s">
-        <v>33</v>
-      </c>
-      <c r="G11" s="12">
-        <v>204.3</v>
-      </c>
-    </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="F11" s="12">
+        <v>46082</v>
+      </c>
+      <c r="G11" s="11">
+        <v>205</v>
+      </c>
+      <c r="K11">
+        <f>I9+I12</f>
+        <v>600</v>
+      </c>
+    </row>
+    <row r="12" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A12" s="1"/>
       <c r="B12" s="1"/>
       <c r="C12" s="3" t="s">
@@ -977,43 +1120,37 @@
       <c r="D12" s="1">
         <v>15</v>
       </c>
-      <c r="F12" s="13" t="s">
-        <v>34</v>
-      </c>
-      <c r="G12" s="12">
+      <c r="F12" s="12">
+        <v>46113</v>
+      </c>
+      <c r="G12" s="11">
         <v>207.1</v>
       </c>
       <c r="I12">
         <v>400</v>
       </c>
     </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A13" s="1"/>
       <c r="B13" s="1"/>
       <c r="C13" s="8" t="s">
         <v>29</v>
       </c>
-      <c r="D13" s="9">
+      <c r="D13" s="1">
         <v>45</v>
       </c>
-      <c r="F13" s="13" t="s">
-        <v>35</v>
-      </c>
-      <c r="G13" s="12">
+      <c r="F13" s="12">
+        <v>46143</v>
+      </c>
+      <c r="G13" s="11">
         <v>208.1</v>
       </c>
     </row>
-    <row r="14" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="C14" s="8" t="s">
-        <v>4</v>
-      </c>
-      <c r="D14" s="9">
-        <v>25</v>
-      </c>
-      <c r="F14" s="13" t="s">
-        <v>36</v>
-      </c>
-      <c r="G14" s="12">
+    <row r="14" spans="1:24" x14ac:dyDescent="0.3">
+      <c r="F14" s="12">
+        <v>46174</v>
+      </c>
+      <c r="G14" s="11">
         <v>207.9</v>
       </c>
       <c r="K14">
@@ -1021,177 +1158,208 @@
         <v>1000</v>
       </c>
     </row>
-    <row r="15" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="F15" s="13" t="s">
-        <v>37</v>
-      </c>
-      <c r="G15" s="12">
+    <row r="15" spans="1:24" x14ac:dyDescent="0.3">
+      <c r="F15" s="12">
+        <v>46204</v>
+      </c>
+      <c r="G15" s="11">
         <v>208.2</v>
       </c>
     </row>
-    <row r="16" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:24" x14ac:dyDescent="0.3">
       <c r="K16">
         <f>I12*6</f>
         <v>2400</v>
       </c>
     </row>
-    <row r="17" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:12" x14ac:dyDescent="0.3">
       <c r="I17">
         <v>1000</v>
       </c>
     </row>
-    <row r="20" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:12" x14ac:dyDescent="0.3">
       <c r="K20">
         <f>I17+55</f>
         <v>1055</v>
       </c>
     </row>
-    <row r="23" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A23" s="15" t="s">
+    <row r="23" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A23" s="13" t="s">
+        <v>33</v>
+      </c>
+      <c r="B23" s="13" t="s">
+        <v>34</v>
+      </c>
+      <c r="C23" s="13" t="s">
+        <v>35</v>
+      </c>
+      <c r="D23" s="13" t="s">
+        <v>36</v>
+      </c>
+      <c r="E23" s="13" t="s">
+        <v>37</v>
+      </c>
+      <c r="F23" s="13" t="s">
         <v>38</v>
       </c>
-      <c r="B23" s="15" t="s">
+    </row>
+    <row r="24" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A24" s="11" t="s">
         <v>39</v>
       </c>
-      <c r="C23" s="15" t="s">
+      <c r="B24" s="11" t="s">
+        <v>45</v>
+      </c>
+      <c r="C24" s="11" t="s">
+        <v>47</v>
+      </c>
+      <c r="D24" s="11">
         <v>40</v>
       </c>
-      <c r="D23" s="15" t="s">
+      <c r="E24" s="11">
+        <v>2</v>
+      </c>
+      <c r="F24" s="11">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="25" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A25" s="11" t="s">
+        <v>40</v>
+      </c>
+      <c r="B25" s="11" t="s">
+        <v>46</v>
+      </c>
+      <c r="C25" s="11" t="s">
+        <v>47</v>
+      </c>
+      <c r="D25" s="11">
+        <v>120</v>
+      </c>
+      <c r="E25" s="11">
+        <v>2</v>
+      </c>
+      <c r="F25" s="11">
+        <v>240</v>
+      </c>
+      <c r="J25">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="26" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A26" s="11" t="s">
         <v>41</v>
       </c>
-      <c r="E23" s="15" t="s">
+      <c r="B26" s="11" t="s">
+        <v>45</v>
+      </c>
+      <c r="C26" s="11" t="s">
+        <v>48</v>
+      </c>
+      <c r="D26" s="11">
+        <v>60</v>
+      </c>
+      <c r="E26" s="11">
+        <v>4</v>
+      </c>
+      <c r="F26" s="11">
+        <v>240</v>
+      </c>
+      <c r="L26">
+        <f>J25+J27</f>
+        <v>500</v>
+      </c>
+    </row>
+    <row r="27" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A27" s="11" t="s">
         <v>42</v>
       </c>
-      <c r="F23" s="15" t="s">
+      <c r="B27" s="11" t="s">
+        <v>46</v>
+      </c>
+      <c r="C27" s="11" t="s">
+        <v>48</v>
+      </c>
+      <c r="D27" s="11">
+        <v>100</v>
+      </c>
+      <c r="E27" s="11">
+        <v>3</v>
+      </c>
+      <c r="F27" s="11">
+        <v>300</v>
+      </c>
+      <c r="J27">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="28" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A28" s="11" t="s">
         <v>43</v>
       </c>
-    </row>
-    <row r="24" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A24" s="12" t="s">
+      <c r="B28" s="11" t="s">
+        <v>46</v>
+      </c>
+      <c r="C28" s="11" t="s">
+        <v>47</v>
+      </c>
+      <c r="D28" s="11">
+        <v>120</v>
+      </c>
+      <c r="E28" s="11">
+        <v>6</v>
+      </c>
+      <c r="F28" s="11">
+        <v>720</v>
+      </c>
+    </row>
+    <row r="29" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A29" s="11" t="s">
         <v>44</v>
       </c>
-      <c r="B24" s="12" t="s">
+      <c r="B29" s="11" t="s">
+        <v>46</v>
+      </c>
+      <c r="C29" s="11" t="s">
+        <v>48</v>
+      </c>
+      <c r="D29" s="11">
+        <v>25</v>
+      </c>
+      <c r="E29" s="11">
+        <v>2</v>
+      </c>
+      <c r="F29" s="11">
         <v>50</v>
       </c>
-      <c r="C24" s="12" t="s">
-        <v>52</v>
-      </c>
-      <c r="D24" s="12">
-        <v>40</v>
-      </c>
-      <c r="E24" s="12">
-        <v>2</v>
-      </c>
-      <c r="F24" s="16">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="25" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A25" s="12" t="s">
-        <v>45</v>
-      </c>
-      <c r="B25" s="12" t="s">
-        <v>51</v>
-      </c>
-      <c r="C25" s="12" t="s">
-        <v>52</v>
-      </c>
-      <c r="D25" s="12">
-        <v>120</v>
-      </c>
-      <c r="E25" s="12">
-        <v>2</v>
-      </c>
-      <c r="F25" s="16">
-        <v>240</v>
-      </c>
-    </row>
-    <row r="26" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A26" s="12" t="s">
-        <v>46</v>
-      </c>
-      <c r="B26" s="12" t="s">
-        <v>50</v>
-      </c>
-      <c r="C26" s="12" t="s">
-        <v>53</v>
-      </c>
-      <c r="D26" s="12">
-        <v>60</v>
-      </c>
-      <c r="E26" s="12">
-        <v>4</v>
-      </c>
-      <c r="F26" s="16">
-        <v>240</v>
-      </c>
-    </row>
-    <row r="27" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A27" s="12" t="s">
-        <v>47</v>
-      </c>
-      <c r="B27" s="12" t="s">
-        <v>51</v>
-      </c>
-      <c r="C27" s="12" t="s">
-        <v>53</v>
-      </c>
-      <c r="D27" s="12">
-        <v>100</v>
-      </c>
-      <c r="E27" s="12">
-        <v>3</v>
-      </c>
-      <c r="F27" s="16">
-        <v>300</v>
-      </c>
-    </row>
-    <row r="28" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A28" s="12" t="s">
-        <v>48</v>
-      </c>
-      <c r="B28" s="12" t="s">
-        <v>51</v>
-      </c>
-      <c r="C28" s="12" t="s">
-        <v>52</v>
-      </c>
-      <c r="D28" s="12">
-        <v>120</v>
-      </c>
-      <c r="E28" s="12">
-        <v>6</v>
-      </c>
-      <c r="F28" s="16">
-        <v>720</v>
-      </c>
-    </row>
-    <row r="29" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A29" s="12" t="s">
-        <v>49</v>
-      </c>
-      <c r="B29" s="12" t="s">
-        <v>51</v>
-      </c>
-      <c r="C29" s="12" t="s">
-        <v>53</v>
-      </c>
-      <c r="D29" s="12">
-        <v>25</v>
-      </c>
-      <c r="E29" s="12">
-        <v>2</v>
-      </c>
-      <c r="F29" s="16">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="30" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A30" s="12"/>
+    </row>
+    <row r="30" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A30" s="13"/>
+      <c r="B30" s="13"/>
+      <c r="C30" s="13"/>
+      <c r="D30" s="13"/>
+      <c r="E30" s="13"/>
+      <c r="F30" s="13"/>
+    </row>
+    <row r="31" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A31" s="11"/>
+      <c r="B31" s="11"/>
+      <c r="C31" s="11"/>
+      <c r="D31" s="11"/>
+      <c r="E31" s="11"/>
+      <c r="F31" s="11"/>
+    </row>
+    <row r="32" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A32" s="11"/>
+      <c r="B32" s="11"/>
+      <c r="C32" s="11"/>
+      <c r="D32" s="11"/>
+      <c r="E32" s="11"/>
+      <c r="F32" s="11"/>
     </row>
   </sheetData>
   <phoneticPr fontId="3" type="noConversion"/>
-  <conditionalFormatting sqref="D8:D14">
+  <conditionalFormatting sqref="D8:D13">
     <cfRule type="dataBar" priority="4">
       <dataBar>
         <cfvo type="min"/>
@@ -1228,19 +1396,10 @@
               <x14:axisColor rgb="FF000000"/>
             </x14:dataBar>
           </x14:cfRule>
-          <xm:sqref>D8:D14</xm:sqref>
+          <xm:sqref>D8:D13</xm:sqref>
         </x14:conditionalFormatting>
       </x14:conditionalFormattings>
     </ext>
   </extLst>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0AB9FC98-78AE-4240-86AF-DAC89B581F95}">
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
-  <sheetData/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
 </file>